--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484825_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484825_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.876</v>
+        <v>3.1393</v>
       </c>
       <c r="E2" t="n">
-        <v>3.7402</v>
+        <v>2.8448</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1358</v>
+        <v>0.2946</v>
       </c>
       <c r="G2" t="n">
         <v>-0.4855</v>
@@ -610,13 +610,13 @@
         <v>2.0757</v>
       </c>
       <c r="S2" t="n">
-        <v>1.2409</v>
+        <v>0.5042</v>
       </c>
       <c r="T2" t="n">
-        <v>1.0204</v>
+        <v>0.125</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2205</v>
+        <v>0.3792</v>
       </c>
       <c r="V2" t="n">
         <v>3.3093</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.0849</v>
+        <v>2.8068</v>
       </c>
       <c r="E3" t="n">
-        <v>1.6756</v>
+        <v>1.3446</v>
       </c>
       <c r="F3" t="n">
-        <v>1.4093</v>
+        <v>1.4622</v>
       </c>
       <c r="G3" t="n">
         <v>1.6111</v>
@@ -688,13 +688,13 @@
         <v>1.3209</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1528</v>
+        <v>-0.1252</v>
       </c>
       <c r="T3" t="n">
-        <v>0.4267</v>
+        <v>0.0958</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2739</v>
+        <v>-0.221</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.5248</v>
+        <v>1.5908</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4148</v>
+        <v>0.8247</v>
       </c>
       <c r="F4" t="n">
-        <v>1.11</v>
+        <v>0.7661</v>
       </c>
       <c r="G4" t="n">
         <v>0.1007</v>
@@ -766,13 +766,13 @@
         <v>2.2644</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.161</v>
+        <v>-0.0951</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.7984</v>
+        <v>-0.3885</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6373</v>
+        <v>0.2934</v>
       </c>
       <c r="V4" t="n">
         <v>-0.3018</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8141</v>
+        <v>1.1026</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3283</v>
+        <v>0.4845</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4858</v>
+        <v>0.6181</v>
       </c>
       <c r="G5" t="n">
         <v>1.4784</v>
@@ -844,13 +844,13 @@
         <v>1.5096</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.4191</v>
+        <v>-0.1306</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1052</v>
+        <v>0.051</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3139</v>
+        <v>-0.1816</v>
       </c>
       <c r="V5" t="n">
         <v>-0.6226</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.5393</v>
+        <v>0.0571</v>
       </c>
       <c r="E6" t="n">
-        <v>1.2331</v>
+        <v>1.9353</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.7724</v>
+        <v>-1.8782</v>
       </c>
       <c r="G6" t="n">
         <v>0.9196</v>
@@ -922,13 +922,13 @@
         <v>1.1322</v>
       </c>
       <c r="S6" t="n">
-        <v>0.08110000000000001</v>
+        <v>0.6775</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.7519</v>
+        <v>-0.0497</v>
       </c>
       <c r="U6" t="n">
-        <v>0.833</v>
+        <v>0.7272</v>
       </c>
       <c r="V6" t="n">
         <v>0.1583</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>R. AGBEKO</t>
+          <t>S. JIMENA LLORCA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.9433</v>
+        <v>0.0503</v>
       </c>
       <c r="E7" t="n">
-        <v>1.3487</v>
+        <v>1.6101</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.2919</v>
+        <v>-1.5597</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8671</v>
+        <v>1.687</v>
       </c>
       <c r="H7" t="n">
-        <v>0.9383</v>
+        <v>0.414</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.0712</v>
+        <v>1.273</v>
       </c>
       <c r="J7" t="n">
-        <v>2.8178</v>
+        <v>4.0496</v>
       </c>
       <c r="K7" t="n">
-        <v>2.6945</v>
+        <v>1.976</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1234</v>
+        <v>2.0735</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.9507</v>
+        <v>-2.3625</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.7561</v>
+        <v>-1.562</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.1946</v>
+        <v>-0.8005</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.3209</v>
+        <v>0.1887</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.0757</v>
+        <v>-2.2644</v>
       </c>
       <c r="R7" t="n">
-        <v>0.7548</v>
+        <v>2.4531</v>
       </c>
       <c r="S7" t="n">
-        <v>0.5784</v>
+        <v>-0.1539</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0029</v>
+        <v>-0.1751</v>
       </c>
       <c r="U7" t="n">
-        <v>0.5755</v>
+        <v>0.0212</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.0679</v>
+        <v>-1.6715</v>
       </c>
       <c r="W7" t="n">
-        <v>0.6036</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
         <v>-1.6715</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S. JIMENA LLORCA</t>
+          <t>R. AGBEKO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.0403</v>
+        <v>-0.8257</v>
       </c>
       <c r="E8" t="n">
-        <v>0.8105</v>
+        <v>1.4662</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.8507</v>
+        <v>-2.2919</v>
       </c>
       <c r="G8" t="n">
-        <v>1.687</v>
+        <v>0.8671</v>
       </c>
       <c r="H8" t="n">
-        <v>0.414</v>
+        <v>0.9383</v>
       </c>
       <c r="I8" t="n">
-        <v>1.273</v>
+        <v>-0.0712</v>
       </c>
       <c r="J8" t="n">
-        <v>4.0496</v>
+        <v>2.8178</v>
       </c>
       <c r="K8" t="n">
-        <v>1.976</v>
+        <v>2.6945</v>
       </c>
       <c r="L8" t="n">
-        <v>2.0735</v>
+        <v>0.1234</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.3625</v>
+        <v>-1.9507</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.562</v>
+        <v>-1.7561</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.8005</v>
+        <v>-0.1946</v>
       </c>
       <c r="P8" t="n">
-        <v>0.1887</v>
+        <v>-1.3209</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.2644</v>
+        <v>-2.0757</v>
       </c>
       <c r="R8" t="n">
-        <v>2.4531</v>
+        <v>0.7548</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.2445</v>
+        <v>0.696</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.9747</v>
+        <v>0.1205</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2698</v>
+        <v>0.5755</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.6715</v>
+        <v>-1.0679</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.6036</v>
       </c>
       <c r="X8" t="n">
         <v>-1.6715</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.8597</v>
+        <v>-1.4125</v>
       </c>
       <c r="E10" t="n">
-        <v>1.7616</v>
+        <v>1.9178</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.6213</v>
+        <v>-3.3303</v>
       </c>
       <c r="G10" t="n">
         <v>0.2225</v>
@@ -1234,13 +1234,13 @@
         <v>1.6983</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3351</v>
+        <v>0.1121</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3498</v>
+        <v>-0.1936</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0147</v>
+        <v>0.3057</v>
       </c>
       <c r="V10" t="n">
         <v>-1.3697</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.9983</v>
+        <v>-4.7079</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.9331</v>
+        <v>-3.1666</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.0651</v>
+        <v>-1.5413</v>
       </c>
       <c r="G11" t="n">
         <v>-0.768</v>
@@ -1312,13 +1312,13 @@
         <v>1.887</v>
       </c>
       <c r="S11" t="n">
-        <v>1.6378</v>
+        <v>0.9281</v>
       </c>
       <c r="T11" t="n">
-        <v>0.6771</v>
+        <v>0.4436</v>
       </c>
       <c r="U11" t="n">
-        <v>0.9606</v>
+        <v>0.4845</v>
       </c>
       <c r="V11" t="n">
         <v>-1.8488</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.3262999999999994</v>
+        <v>0.5556000000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>8.379700000000001</v>
+        <v>9.261399999999998</v>
       </c>
       <c r="F12" t="n">
-        <v>-8.7057</v>
+        <v>-8.705599999999999</v>
       </c>
       <c r="G12" t="n">
         <v>5.6329</v>
@@ -1390,13 +1390,13 @@
         <v>15.096</v>
       </c>
       <c r="S12" t="n">
-        <v>1.5313</v>
+        <v>2.4131</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.8528999999999998</v>
+        <v>0.02899999999999997</v>
       </c>
       <c r="U12" t="n">
-        <v>2.384</v>
+        <v>2.3841</v>
       </c>
       <c r="V12" t="n">
         <v>-4.6599</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>11.5736</v>
+        <v>12.1906</v>
       </c>
       <c r="E13" t="n">
-        <v>10.1217</v>
+        <v>10.6088</v>
       </c>
       <c r="F13" t="n">
-        <v>1.4519</v>
+        <v>1.5818</v>
       </c>
       <c r="G13" t="n">
         <v>5.7494</v>
@@ -1468,13 +1468,13 @@
         <v>3.0192</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.5908</v>
+        <v>0.0263</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.9747</v>
+        <v>-0.4875</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3839</v>
+        <v>0.5139</v>
       </c>
       <c r="V13" t="n">
         <v>4.3392</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.503</v>
+        <v>6.2162</v>
       </c>
       <c r="E14" t="n">
-        <v>7.2178</v>
+        <v>7.5101</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.7148</v>
+        <v>-1.2939</v>
       </c>
       <c r="G14" t="n">
         <v>3.7352</v>
@@ -1546,13 +1546,13 @@
         <v>3.2079</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.4208</v>
+        <v>-0.7076</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.1511</v>
+        <v>-0.8588</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2698</v>
+        <v>0.1512</v>
       </c>
       <c r="V14" t="n">
         <v>1.8678</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.843</v>
+        <v>1.1576</v>
       </c>
       <c r="E15" t="n">
-        <v>1.7837</v>
+        <v>1.3939</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0594</v>
+        <v>-0.2364</v>
       </c>
       <c r="G15" t="n">
         <v>-0.7020999999999999</v>
@@ -1624,13 +1624,13 @@
         <v>2.0757</v>
       </c>
       <c r="S15" t="n">
-        <v>1.7148</v>
+        <v>1.0293</v>
       </c>
       <c r="T15" t="n">
-        <v>0.5596</v>
+        <v>0.1698</v>
       </c>
       <c r="U15" t="n">
-        <v>1.1552</v>
+        <v>0.8595</v>
       </c>
       <c r="V15" t="n">
         <v>-0.3018</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.2589</v>
+        <v>1.0269</v>
       </c>
       <c r="E16" t="n">
-        <v>0.1086</v>
+        <v>0.0112</v>
       </c>
       <c r="F16" t="n">
-        <v>1.1503</v>
+        <v>1.0157</v>
       </c>
       <c r="G16" t="n">
         <v>1.1096</v>
@@ -1702,13 +1702,13 @@
         <v>3.0192</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2816</v>
+        <v>0.0495</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.3839</v>
+        <v>-0.4814</v>
       </c>
       <c r="U16" t="n">
-        <v>0.6655</v>
+        <v>0.5309</v>
       </c>
       <c r="V16" t="n">
         <v>1.566</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.9482</v>
+        <v>-1.1527</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9467</v>
+        <v>0.5569</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.8949</v>
+        <v>-1.7097</v>
       </c>
       <c r="G18" t="n">
         <v>-1.8591</v>
@@ -1858,13 +1858,13 @@
         <v>1.887</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3345</v>
+        <v>-0.5391</v>
       </c>
       <c r="T18" t="n">
-        <v>0.0029</v>
+        <v>-0.3868</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3374</v>
+        <v>-0.1522</v>
       </c>
       <c r="V18" t="n">
         <v>-0.6415999999999999</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D. MARTINEZ JURADO</t>
+          <t>O. CASTRILLON RODRIGUEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.4706</v>
+        <v>-1.9006</v>
       </c>
       <c r="E19" t="n">
-        <v>1.0337</v>
+        <v>-0.5704</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.5043</v>
+        <v>-1.3302</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4837</v>
+        <v>-2.2675</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.2958</v>
+        <v>-0.6785</v>
       </c>
       <c r="I19" t="n">
-        <v>0.7795</v>
+        <v>-1.589</v>
       </c>
       <c r="J19" t="n">
-        <v>0.972</v>
+        <v>-0.6909</v>
       </c>
       <c r="K19" t="n">
-        <v>0.972</v>
+        <v>0.4437</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>-1.1346</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.4883</v>
+        <v>-1.5767</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.2678</v>
+        <v>-1.1222</v>
       </c>
       <c r="O19" t="n">
-        <v>0.7795</v>
+        <v>-0.4544</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.7548</v>
+        <v>0.9435</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9435</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.1887</v>
+        <v>0.9435</v>
       </c>
       <c r="S19" t="n">
-        <v>0.6684</v>
+        <v>0.027</v>
       </c>
       <c r="T19" t="n">
-        <v>1.0052</v>
+        <v>0.1205</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3368</v>
+        <v>-0.0934</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.8678</v>
+        <v>-0.6036</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.8678</v>
+        <v>-0.6036</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>G. FONT FENOLLAR</t>
+          <t>D. MARTINEZ JURADO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.497</v>
+        <v>-1.9434</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.6518</v>
+        <v>0.3516</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.8452</v>
+        <v>-2.295</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.5535</v>
+        <v>0.4837</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.8609</v>
+        <v>-0.2958</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.6927</v>
+        <v>0.7795</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.6496</v>
+        <v>0.972</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.6496</v>
+        <v>0.972</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.904</v>
+        <v>-0.4883</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.2113</v>
+        <v>-1.2678</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.6927</v>
+        <v>0.7795</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.9435</v>
+        <v>-0.7548</v>
       </c>
       <c r="Q20" t="n">
         <v>-0.9435</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>0.1887</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>0.1956</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0588</v>
+        <v>0.3231</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0588</v>
+        <v>-0.1276</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-1.8678</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-1.8678</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>O. CASTRILLON RODRIGUEZ</t>
+          <t>G. FONT FENOLLAR</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.4996</v>
+        <v>-2.497</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.9601</v>
+        <v>-1.6518</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.5395</v>
+        <v>-0.8452</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.2675</v>
+        <v>-1.5535</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.6785</v>
+        <v>-0.8609</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.589</v>
+        <v>-0.6927</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.6909</v>
+        <v>-0.6496</v>
       </c>
       <c r="K21" t="n">
-        <v>0.4437</v>
+        <v>-0.6496</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.1346</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.5767</v>
+        <v>-0.904</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.1222</v>
+        <v>-0.2113</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.4544</v>
+        <v>-0.6927</v>
       </c>
       <c r="P21" t="n">
-        <v>0.9435</v>
+        <v>-0.9435</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-0.9435</v>
       </c>
       <c r="R21" t="n">
-        <v>0.9435</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.572</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2693</v>
+        <v>-0.0588</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3027</v>
+        <v>0.0588</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.6036</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.6036</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.8872</v>
+        <v>-4.4952</v>
       </c>
       <c r="E22" t="n">
         <v>-5.1085</v>
       </c>
       <c r="F22" t="n">
-        <v>0.2213</v>
+        <v>0.6133</v>
       </c>
       <c r="G22" t="n">
         <v>-6.564</v>
@@ -2170,13 +2170,13 @@
         <v>2.8305</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.512</v>
+        <v>-0.1199</v>
       </c>
       <c r="T22" t="n">
         <v>-0.585</v>
       </c>
       <c r="U22" t="n">
-        <v>0.07290000000000001</v>
+        <v>0.465</v>
       </c>
       <c r="V22" t="n">
         <v>0.3018</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.6456</v>
+        <v>-6.0731</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.7271</v>
+        <v>-4.3373</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.9186</v>
+        <v>-1.7358</v>
       </c>
       <c r="G23" t="n">
         <v>-2.8605</v>
@@ -2248,13 +2248,13 @@
         <v>0.7548</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.766</v>
+        <v>-0.1934</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.4703</v>
+        <v>-0.0806</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2957</v>
+        <v>-0.1129</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>0.326299999999998</v>
+        <v>1.6253</v>
       </c>
       <c r="E24" t="n">
-        <v>8.7059</v>
+        <v>8.7057</v>
       </c>
       <c r="F24" t="n">
-        <v>-8.3796</v>
+        <v>-7.0806</v>
       </c>
       <c r="G24" t="n">
         <v>-5.6328</v>
@@ -2296,13 +2296,13 @@
         <v>-2.2773</v>
       </c>
       <c r="I24" t="n">
-        <v>-3.355600000000001</v>
+        <v>-3.3556</v>
       </c>
       <c r="J24" t="n">
         <v>13.791</v>
       </c>
       <c r="K24" t="n">
-        <v>9.680499999999999</v>
+        <v>9.6805</v>
       </c>
       <c r="L24" t="n">
         <v>4.110399999999999</v>
@@ -2314,7 +2314,7 @@
         <v>-11.9578</v>
       </c>
       <c r="O24" t="n">
-        <v>-7.465800000000001</v>
+        <v>-7.465800000000002</v>
       </c>
       <c r="P24" t="n">
         <v>2.8305</v>
@@ -2326,13 +2326,13 @@
         <v>17.9265</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.5313</v>
+        <v>-0.2322999999999998</v>
       </c>
       <c r="T24" t="n">
-        <v>-2.384199999999999</v>
+        <v>-2.3843</v>
       </c>
       <c r="U24" t="n">
-        <v>0.8527</v>
+        <v>2.152</v>
       </c>
       <c r="V24" t="n">
         <v>4.66</v>
